--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104731_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104731_W31.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9719</v>
+        <v>2.8352</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8258</v>
+        <v>4.5835</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8539</v>
+        <v>-1.7483</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5069</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0955</v>
+        <v>-1.0943</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6031</v>
+        <v>1.6012</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2225</v>
+        <v>2.2145</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6627</v>
+        <v>0.6583</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5598</v>
+        <v>1.5563</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7149</v>
+        <v>-1.7077</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7582</v>
+        <v>-1.7526</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0433</v>
+        <v>0.0449</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3283</v>
+        <v>1.1902</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7392</v>
+        <v>1.5071</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4109</v>
+        <v>-0.317</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1433</v>
+        <v>2.7076</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1919</v>
+        <v>3.2274</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0486</v>
+        <v>-0.5198</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5015</v>
+        <v>1.4988</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1399</v>
+        <v>2.1294</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6384</v>
+        <v>-0.6306</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1074</v>
+        <v>4.0887</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9582</v>
+        <v>3.9398</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1491</v>
+        <v>0.1489</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6059</v>
+        <v>-2.5899</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8183</v>
+        <v>-1.8103</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7875</v>
+        <v>-0.7796</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4078</v>
+        <v>3.4145</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3586</v>
+        <v>-0.7896</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5992</v>
+        <v>-0.5347</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2407</v>
+        <v>-0.2549</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8603</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9557</v>
+        <v>1.9497</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4366</v>
+        <v>0.7706</v>
       </c>
       <c r="E4" t="n">
-        <v>0.966</v>
+        <v>1.4528</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5294</v>
+        <v>-0.6822</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7457</v>
+        <v>-0.4931</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7191</v>
+        <v>1.3328</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0266</v>
+        <v>-1.8259</v>
       </c>
       <c r="J4" t="n">
-        <v>2.821</v>
+        <v>2.0547</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3796</v>
+        <v>3.1576</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4414</v>
+        <v>-1.1029</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0753</v>
+        <v>-2.5478</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6605</v>
+        <v>-1.8248</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4147</v>
+        <v>-0.723</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2272</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2719</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4991</v>
+        <v>2.7316</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5363</v>
+        <v>-1.4192</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4169</v>
+        <v>-0.5532</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-0.8659</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1653</v>
+        <v>0.2272</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9331</v>
+        <v>0.4211</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7679</v>
+        <v>-0.1939</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4943</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3352</v>
+        <v>0.7156</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8294</v>
+        <v>0.032</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0694</v>
+        <v>2.8071</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1685</v>
+        <v>2.368</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.0991</v>
+        <v>0.4392</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5636</v>
+        <v>-2.0596</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8334</v>
+        <v>-1.6524</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-0.4072</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5903</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7262</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.022</v>
+        <v>-0.748</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0915</v>
+        <v>-0.1097</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9305</v>
+        <v>-0.6383</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1456</v>
+        <v>0.2246</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12</v>
+        <v>0.0667</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0256</v>
+        <v>0.158</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7617</v>
+        <v>-1.7612</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2337</v>
+        <v>-1.2322</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5279</v>
+        <v>-0.529</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1108</v>
+        <v>-1.1154</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1668</v>
+        <v>-0.1691</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.944</v>
+        <v>-0.9463</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6508</v>
+        <v>-0.6458</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0669</v>
+        <v>-1.0631</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4161</v>
+        <v>0.4173</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.0753</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2308</v>
+        <v>1.182</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2323</v>
+        <v>-0.1067</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2177</v>
+        <v>-0.0078</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2702</v>
+        <v>-0.4553</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0526</v>
+        <v>0.4475</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4798</v>
+        <v>-0.4748</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0211</v>
+        <v>-0.0177</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4587</v>
+        <v>-0.4571</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1626</v>
+        <v>1.1546</v>
       </c>
       <c r="K7" t="n">
-        <v>1.106</v>
+        <v>1.1032</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0566</v>
+        <v>0.0515</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6423</v>
+        <v>-1.6295</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1271</v>
+        <v>-1.1209</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5153</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9534</v>
+        <v>2.9592</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5107</v>
+        <v>-1.3053</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2522</v>
+        <v>-0.4231</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2585</v>
+        <v>-0.8823</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.272</v>
+        <v>-1.9406</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1507</v>
+        <v>-0.4963</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4227</v>
+        <v>-1.4444</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0074</v>
+        <v>-2.003</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2636</v>
       </c>
       <c r="I8" t="n">
-        <v>0.261</v>
+        <v>0.2607</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.8256</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6679</v>
+        <v>-0.669</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1551</v>
+        <v>-0.1566</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1843</v>
+        <v>-1.1774</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6004</v>
+        <v>-1.5946</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4161</v>
+        <v>0.4173</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>2.0303</v>
+        <v>1.3598</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1775</v>
+        <v>1.5374</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1471</v>
+        <v>-0.1775</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.7146</v>
+        <v>-4.2611</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.9984</v>
+        <v>-4.0637</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2838</v>
+        <v>-0.1974</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.5957</v>
+        <v>-4.5911</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0459</v>
+        <v>-2.0423</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5498</v>
+        <v>-2.5488</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.8689</v>
+        <v>-3.8775</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5582</v>
+        <v>-0.5623</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.3107</v>
+        <v>-3.3152</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7268</v>
+        <v>-0.7136</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4877</v>
+        <v>-1.48</v>
       </c>
       <c r="O9" t="n">
-        <v>0.761</v>
+        <v>0.7664</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5733</v>
+        <v>-0.1253</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9023</v>
+        <v>0.0414</v>
       </c>
       <c r="U9" t="n">
-        <v>0.329</v>
+        <v>-0.1667</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5572</v>
+        <v>-4.5379</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3416</v>
+        <v>-3.4629</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2156</v>
+        <v>-1.075</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.7192</v>
+        <v>-4.7212</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.541</v>
+        <v>-1.542</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.1782</v>
+        <v>-3.1792</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1674</v>
+        <v>-1.1793</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7206</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.888</v>
+        <v>-1.8925</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.5518</v>
+        <v>-3.5419</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.2616</v>
+        <v>-2.2552</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2902</v>
+        <v>-1.2866</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7262</v>
+        <v>2.7316</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0652</v>
+        <v>-0.0444</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6751</v>
+        <v>0.2203</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3901</v>
+        <v>-0.2647</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.1884</v>
+        <v>-8.4087</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.3836</v>
+        <v>-6.5622</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8048</v>
+        <v>-1.8465</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8257</v>
+        <v>-3.8282</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5109</v>
+        <v>-1.5131</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3148</v>
+        <v>-2.315</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5905</v>
+        <v>-1.605</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9686</v>
+        <v>0.9578</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5591</v>
+        <v>-2.5628</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2352</v>
+        <v>-2.2232</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.4795</v>
+        <v>-2.4709</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2443</v>
+        <v>0.2477</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.3166</v>
+        <v>-4.325</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.9069</v>
+        <v>-5.9184</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2045</v>
+        <v>0.9917</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1138</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0907</v>
+        <v>0.0305</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.0872</v>
+        <v>-12.3909</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8063</v>
+        <v>-5.288899999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.2809</v>
+        <v>-7.102</v>
       </c>
       <c r="G12" t="n">
-        <v>-15.129</v>
+        <v>-15.1194</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.522199999999998</v>
+        <v>-5.527399999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.6065</v>
+        <v>-9.591699999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8222</v>
+        <v>3.716800000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>11.5713</v>
+        <v>11.4975</v>
       </c>
       <c r="L12" t="n">
-        <v>-7.749099999999999</v>
+        <v>-7.7804</v>
       </c>
       <c r="M12" t="n">
-        <v>-18.9509</v>
+        <v>-18.8364</v>
       </c>
       <c r="N12" t="n">
-        <v>-17.0936</v>
+        <v>-17.0248</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8572</v>
+        <v>-1.8114</v>
       </c>
       <c r="P12" t="n">
-        <v>1.135899999999999</v>
+        <v>1.138199999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-18.1751</v>
+        <v>-18.2104</v>
       </c>
       <c r="R12" t="n">
-        <v>19.3108</v>
+        <v>19.3487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5044999999999999</v>
+        <v>0.1851999999999996</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1579</v>
+        <v>3.8287</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.6621</v>
+        <v>-3.6435</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4101</v>
+        <v>1.405099999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>5.388999999999999</v>
+        <v>5.376</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.978899999999999</v>
+        <v>-3.9709</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7331</v>
+        <v>4.0159</v>
       </c>
       <c r="E13" t="n">
-        <v>3.104</v>
+        <v>3.0842</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6291</v>
+        <v>0.9316</v>
       </c>
       <c r="G13" t="n">
-        <v>3.359</v>
+        <v>3.354</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1541</v>
+        <v>1.1544</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2049</v>
+        <v>2.1996</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2839</v>
+        <v>4.2692</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3194</v>
+        <v>1.3133</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9645</v>
+        <v>2.9559</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.925</v>
+        <v>-0.9152</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1654</v>
+        <v>-0.1588</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.7563</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4654</v>
+        <v>1.7513</v>
       </c>
       <c r="T13" t="n">
-        <v>1.092</v>
+        <v>1.0914</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3734</v>
+        <v>0.66</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4147</v>
+        <v>2.96</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9176</v>
+        <v>3.1978</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5029</v>
+        <v>-0.2378</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1651</v>
+        <v>2.1647</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3869</v>
+        <v>0.3876</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7782</v>
+        <v>1.7771</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1033</v>
+        <v>3.0959</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4689</v>
+        <v>1.4651</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6344</v>
+        <v>1.6308</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9382</v>
+        <v>-0.9312</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.082</v>
+        <v>-1.0775</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1438</v>
+        <v>0.1463</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1136</v>
+        <v>1.6572</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9503</v>
+        <v>1.24</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1633</v>
+        <v>0.4171</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7849</v>
+        <v>2.7382</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2215</v>
+        <v>0.5561</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5634</v>
+        <v>2.1821</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7216</v>
+        <v>-0.7198</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2743</v>
+        <v>-0.273</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4474</v>
+        <v>-0.4468</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1508</v>
+        <v>0.1385</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1008</v>
+        <v>1.0924</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.95</v>
+        <v>-0.9539</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8724</v>
+        <v>-0.8583</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.375</v>
+        <v>-1.3654</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5026</v>
+        <v>0.5071</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5747</v>
+        <v>0.5263</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.044</v>
+        <v>0.3085</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6187</v>
+        <v>0.2178</v>
       </c>
       <c r="V15" t="n">
-        <v>2.0231</v>
+        <v>2.0212</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4883</v>
+        <v>2.4377</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1369</v>
+        <v>0.8734</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3514</v>
+        <v>1.5643</v>
       </c>
       <c r="G16" t="n">
-        <v>5.044</v>
+        <v>5.0423</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0707</v>
+        <v>3.07</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9732</v>
+        <v>1.9722</v>
       </c>
       <c r="J16" t="n">
-        <v>4.5697</v>
+        <v>4.5531</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4758</v>
+        <v>4.4643</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0939</v>
+        <v>0.0887</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4743</v>
+        <v>0.4892</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4051</v>
+        <v>-1.3943</v>
       </c>
       <c r="O16" t="n">
-        <v>1.8794</v>
+        <v>1.8835</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2604</v>
+        <v>-1.3086</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.025</v>
+        <v>-0.2652</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2354</v>
+        <v>-1.0435</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3533</v>
+        <v>1.4784</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3835</v>
+        <v>0.6452</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9698</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6209</v>
+        <v>2.6109</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1179</v>
+        <v>-0.1253</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7388</v>
+        <v>2.7363</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1026</v>
+        <v>2.0812</v>
       </c>
       <c r="K17" t="n">
-        <v>2.046</v>
+        <v>2.0297</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0566</v>
+        <v>0.0515</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5183</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.1639</v>
+        <v>-2.1551</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6823</v>
+        <v>2.6848</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0508</v>
+        <v>0.1846</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5528</v>
+        <v>0.8403</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.502</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8121</v>
+        <v>1.0332</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5456</v>
+        <v>1.2138</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2665</v>
+        <v>-0.1806</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1913</v>
+        <v>3.4639</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5229</v>
+        <v>0.1318</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6684</v>
+        <v>3.332</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5903</v>
+        <v>4.812</v>
       </c>
       <c r="K18" t="n">
-        <v>0.553</v>
+        <v>2.258</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>2.554</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6011</v>
+        <v>-1.3481</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0301</v>
+        <v>-2.1262</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6311</v>
+        <v>0.778</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9087</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1359</v>
+        <v>-3.4145</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2272</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5617</v>
+        <v>-0.382</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.1838</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5617</v>
+        <v>-0.1983</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6525</v>
+        <v>0.8086</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8802</v>
+        <v>0.5401</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2276</v>
+        <v>0.2685</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4653</v>
+        <v>1.1916</v>
       </c>
       <c r="H19" t="n">
-        <v>0.13</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>3.3353</v>
+        <v>0.669</v>
       </c>
       <c r="J19" t="n">
-        <v>4.8243</v>
+        <v>0.5888</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2638</v>
+        <v>0.5516</v>
       </c>
       <c r="L19" t="n">
-        <v>2.5604</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.359</v>
+        <v>0.6028</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.1339</v>
+        <v>-0.0289</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7749</v>
+        <v>0.6317</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.0447</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4078</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3631</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7681</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5363</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2318</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3372</v>
+        <v>0.0221</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5757</v>
+        <v>-1.2358</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2385</v>
+        <v>1.2579</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6682</v>
+        <v>-0.6645</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2074</v>
+        <v>-1.2038</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5392</v>
+        <v>0.5393</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2409</v>
+        <v>-0.2495</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0052</v>
+        <v>-0.0107</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2357</v>
+        <v>-0.2388</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4273</v>
+        <v>-0.415</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2022</v>
+        <v>-1.1931</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7749</v>
+        <v>0.778</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1234</v>
+        <v>-0.7687</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.3929</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3789</v>
+        <v>-0.3758</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7793</v>
+        <v>-0.0766</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0533</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>1.274</v>
+        <v>0.555</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1343</v>
+        <v>-0.5051</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5417999999999999</v>
+        <v>2.8949</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4074</v>
+        <v>-3.4</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2423</v>
+        <v>-0.1783</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3975</v>
+        <v>3.4129</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6398</v>
+        <v>-3.5912</v>
       </c>
       <c r="M21" t="n">
-        <v>0.108</v>
+        <v>-0.3268</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9392</v>
+        <v>-0.518</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0472</v>
+        <v>0.1912</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6816</v>
+        <v>1.1382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2719</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5903</v>
+        <v>2.2763</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0366</v>
+        <v>0.3798</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4608</v>
+        <v>0.6848</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4243</v>
+        <v>-0.305</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-0.679</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1675</v>
+        <v>-0.0514</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7593</v>
+        <v>-0.6276</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6917</v>
+        <v>-0.6894</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4967</v>
+        <v>-0.4943</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1951</v>
+        <v>-0.1952</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0287</v>
+        <v>-0.0304</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0518</v>
+        <v>0.0517</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0806</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.663</v>
+        <v>-0.659</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5485</v>
+        <v>-0.546</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1145</v>
+        <v>-0.113</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3711</v>
+        <v>-0.1277</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1388</v>
+        <v>-0.021</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2323</v>
+        <v>-0.1067</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1082</v>
+        <v>-0.8609</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2031</v>
+        <v>-2.1794</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0949</v>
+        <v>1.3184</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5009</v>
+        <v>-0.1293</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8957</v>
+        <v>-0.5376</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.3966</v>
+        <v>0.4083</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.162</v>
+        <v>-0.2442</v>
       </c>
       <c r="K23" t="n">
-        <v>3.4217</v>
+        <v>0.3964</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.5837</v>
+        <v>-0.6407</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3389</v>
+        <v>0.1149</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.526</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1871</v>
+        <v>1.049</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1359</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2719</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6519</v>
+        <v>-0.0487</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0948</v>
+        <v>0.3412</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7468</v>
+        <v>-0.3899</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>13.0873</v>
+        <v>13.8776</v>
       </c>
       <c r="E24" t="n">
-        <v>6.189700000000001</v>
+        <v>6.012400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>6.8978</v>
+        <v>7.865</v>
       </c>
       <c r="G24" t="n">
-        <v>15.1289</v>
+        <v>15.1193</v>
       </c>
       <c r="H24" t="n">
-        <v>5.522200000000002</v>
+        <v>5.527399999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>9.606300000000001</v>
+        <v>9.591800000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>18.951</v>
+        <v>18.8363</v>
       </c>
       <c r="K24" t="n">
-        <v>17.0935</v>
+        <v>17.0247</v>
       </c>
       <c r="L24" t="n">
-        <v>1.857300000000001</v>
+        <v>1.811400000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.8221</v>
+        <v>-3.717</v>
       </c>
       <c r="N24" t="n">
-        <v>-11.5713</v>
+        <v>-11.4973</v>
       </c>
       <c r="O24" t="n">
-        <v>7.749200000000001</v>
+        <v>7.7803</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.136</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-19.3108</v>
+        <v>-19.3489</v>
       </c>
       <c r="R24" t="n">
-        <v>18.1751</v>
+        <v>18.2105</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5044999999999998</v>
+        <v>1.3015</v>
       </c>
       <c r="T24" t="n">
-        <v>3.6621</v>
+        <v>3.6433</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.1578</v>
+        <v>-2.342</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4102</v>
+        <v>-1.4051</v>
       </c>
       <c r="W24" t="n">
-        <v>2.8876</v>
+        <v>2.8814</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.2978</v>
+        <v>-4.286599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104731_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104731_W31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-3.9709</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104731_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-4.286599999999999</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
